--- a/server/模板/样品导入模板.xlsx
+++ b/server/模板/样品导入模板.xlsx
@@ -413,7 +413,7 @@
     <col min="12" max="12" width="7.83203125" customWidth="1"/>
     <col min="13" max="13" width="7.83203125" customWidth="1"/>
     <col min="14" max="14" width="9.33203125" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" customWidth="1"/>
     <col min="16" max="16" width="7.83203125" customWidth="1"/>
     <col min="17" max="17" width="10.83203125" customWidth="1"/>
     <col min="18" max="18" width="9.33203125" customWidth="1"/>
@@ -464,7 +464,7 @@
         <v>含税价</v>
       </c>
       <c r="O1" t="str">
-        <v>本价含税</v>
+        <v>未税价</v>
       </c>
       <c r="P1" t="str">
         <v>工厂</v>
